--- a/Electronics/PCBs/Motor Driver/PickAndPlace.xlsx
+++ b/Electronics/PCBs/Motor Driver/PickAndPlace.xlsx
@@ -286,7 +286,7 @@
     <t>35mm</t>
   </si>
   <si>
-    <t>36mm</t>
+    <t>34mm</t>
   </si>
   <si>
     <t>2.2kΩ</t>
@@ -1793,7 +1793,7 @@
         <v>21</v>
       </c>
       <c r="L25">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M25" t="s">
         <v>22</v>
@@ -1837,7 +1837,7 @@
         <v>21</v>
       </c>
       <c r="L26">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M26" t="s">
         <v>22</v>
